--- a/diseases/d045/1990-1994.xlsx
+++ b/diseases/d045/1990-1994.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14518,9 +14413,6 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="S72" t="inlineStr">

--- a/diseases/d045/1990-1994.xlsx
+++ b/diseases/d045/1990-1994.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -795,17 +795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1021,7 +1026,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1029,17 +1034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1177,7 +1187,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1185,17 +1195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1411,7 +1426,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1419,17 +1434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1567,7 +1587,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1575,17 +1595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1801,7 +1826,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1809,17 +1834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1957,7 +1987,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1965,17 +1995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2191,7 +2226,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2199,17 +2234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2347,7 +2387,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2355,17 +2395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2581,7 +2626,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2589,17 +2634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2737,7 +2787,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2971,7 +3026,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +3034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3127,7 +3187,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3135,17 +3195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3361,7 +3426,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3369,17 +3434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3517,7 +3587,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3751,7 +3826,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3907,7 +3987,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3915,17 +3995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4141,7 +4226,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4149,17 +4234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4297,7 +4387,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4305,17 +4395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4531,7 +4626,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4687,7 +4787,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4695,17 +4795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4921,7 +5026,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4929,17 +5034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5077,7 +5187,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5085,17 +5195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5311,7 +5426,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5319,17 +5434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5467,7 +5587,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5475,17 +5595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5701,7 +5826,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5709,17 +5834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5857,7 +5987,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5865,17 +5995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -6091,7 +6226,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -6099,17 +6234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6247,7 +6387,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6255,17 +6395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6481,7 +6626,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6489,17 +6634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6637,7 +6787,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6645,17 +6795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6871,7 +7026,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6879,17 +7034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -7027,7 +7187,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -7035,17 +7195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7261,7 +7426,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -7269,17 +7434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7417,7 +7587,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7425,17 +7595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7651,7 +7826,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7659,17 +7834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7807,7 +7987,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7815,17 +7995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -8041,7 +8226,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -8049,17 +8234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8197,7 +8387,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8205,17 +8395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8431,7 +8626,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8439,17 +8634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8587,7 +8787,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -8595,17 +8795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8821,7 +9026,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8829,17 +9034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8977,7 +9187,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8985,17 +9195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9211,7 +9426,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9219,17 +9434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9367,7 +9587,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9375,17 +9595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9601,7 +9826,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9609,17 +9834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9757,7 +9987,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9765,17 +9995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9991,7 +10226,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9999,17 +10234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10147,7 +10387,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -10155,17 +10395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10381,7 +10626,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -10389,17 +10634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10537,7 +10787,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -10545,17 +10795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10771,7 +11026,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -10779,17 +11034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10927,7 +11187,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -10935,17 +11195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11161,7 +11426,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -11169,17 +11434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -11317,7 +11587,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -11325,17 +11595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -11551,7 +11826,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -11559,17 +11834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -11707,7 +11987,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -11715,17 +11995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -11941,7 +12226,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -11949,17 +12234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS59" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -12097,7 +12387,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -12105,17 +12395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12331,7 +12626,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12339,17 +12634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12487,7 +12787,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -12495,17 +12795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12721,7 +13026,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -12729,17 +13034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -12877,7 +13187,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12885,17 +13195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -13111,7 +13426,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13119,17 +13434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13267,7 +13587,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13275,17 +13595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13501,7 +13826,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13509,17 +13834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13657,7 +13987,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -13665,17 +13995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13891,7 +14226,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -13899,17 +14234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14047,7 +14387,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -14055,17 +14395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14281,7 +14626,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -14289,17 +14634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14437,7 +14787,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -14445,17 +14795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14671,7 +15026,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -14679,17 +15034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
